--- a/artfynd/A 55927-2023 artfynd.xlsx
+++ b/artfynd/A 55927-2023 artfynd.xlsx
@@ -2307,7 +2307,7 @@
         <v>136456627</v>
       </c>
       <c r="B15" t="n">
-        <v>92455</v>
+        <v>92458</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 55927-2023 artfynd.xlsx
+++ b/artfynd/A 55927-2023 artfynd.xlsx
@@ -2307,7 +2307,7 @@
         <v>136456627</v>
       </c>
       <c r="B15" t="n">
-        <v>92458</v>
+        <v>92459</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 55927-2023 artfynd.xlsx
+++ b/artfynd/A 55927-2023 artfynd.xlsx
@@ -2307,7 +2307,7 @@
         <v>136456627</v>
       </c>
       <c r="B15" t="n">
-        <v>92459</v>
+        <v>92464</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 55927-2023 artfynd.xlsx
+++ b/artfynd/A 55927-2023 artfynd.xlsx
@@ -2307,7 +2307,7 @@
         <v>136456627</v>
       </c>
       <c r="B15" t="n">
-        <v>92464</v>
+        <v>92466</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 55927-2023 artfynd.xlsx
+++ b/artfynd/A 55927-2023 artfynd.xlsx
@@ -2307,7 +2307,7 @@
         <v>136456627</v>
       </c>
       <c r="B15" t="n">
-        <v>92466</v>
+        <v>92468</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 55927-2023 artfynd.xlsx
+++ b/artfynd/A 55927-2023 artfynd.xlsx
@@ -2307,7 +2307,7 @@
         <v>136456627</v>
       </c>
       <c r="B15" t="n">
-        <v>92468</v>
+        <v>92470</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 55927-2023 artfynd.xlsx
+++ b/artfynd/A 55927-2023 artfynd.xlsx
@@ -2307,7 +2307,7 @@
         <v>136456627</v>
       </c>
       <c r="B15" t="n">
-        <v>92470</v>
+        <v>92471</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 55927-2023 artfynd.xlsx
+++ b/artfynd/A 55927-2023 artfynd.xlsx
@@ -2307,7 +2307,7 @@
         <v>136456627</v>
       </c>
       <c r="B15" t="n">
-        <v>92471</v>
+        <v>92477</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
